--- a/grade.xlsx
+++ b/grade.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OLD LAPTOP DATA\D DRIVE DATA\D Drive data\Ferro Alloy\FY 2026\2. February '2026\HRC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\1019356\Desktop\Energy Sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8904"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,9 +29,6 @@
     <t>Document No</t>
   </si>
   <si>
-    <t>Grade</t>
-  </si>
-  <si>
     <t>Revision No</t>
   </si>
   <si>
@@ -1407,6 +1404,9 @@
   </si>
   <si>
     <t>LcSiMn</t>
+  </si>
+  <si>
+    <t>Dolvi Grade</t>
   </si>
 </sst>
 </file>
@@ -2305,155 +2305,154 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AI224"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.77734375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.5546875" style="4" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6640625" style="4" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5703125" style="4" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="11.7109375" style="4" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="8" style="4" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="7.109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="7.44140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.77734375" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="7.42578125" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.7109375" style="4" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7" style="4" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.33203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.28515625" style="4" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="7" style="4" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.33203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.21875" style="4" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.5546875" style="4" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="7.44140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="7.77734375" style="4" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="8.109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="8.44140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="8.21875" style="4" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8.5546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.28515625" style="4" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.28515625" style="4" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.5703125" style="4" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.42578125" style="4" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="7.7109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="8.140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="8.42578125" style="4" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="8.28515625" style="4" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8.5703125" style="4" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="8" style="4" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="8.33203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="8.28515625" style="4" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="7" style="4" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="7.33203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="7.28515625" style="4" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="7" style="4" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="7.33203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="7.21875" style="4" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="7.5546875" style="4" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="7.33203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="7.6640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="7.28515625" style="4" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="7.5703125" style="4" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="7.28515625" style="4" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="7.7109375" style="4" bestFit="1" customWidth="1"/>
     <col min="34" max="34" width="11" style="4" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="11.33203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="11.28515625" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="C1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>35</v>
-      </c>
-      <c r="B2" t="s">
-        <v>36</v>
       </c>
       <c r="C2" s="2">
         <v>3</v>
@@ -2525,12 +2524,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3" t="s">
         <v>37</v>
-      </c>
-      <c r="B3" t="s">
-        <v>38</v>
       </c>
       <c r="C3" s="2">
         <v>10</v>
@@ -2608,12 +2607,12 @@
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" t="s">
         <v>39</v>
-      </c>
-      <c r="B4" t="s">
-        <v>40</v>
       </c>
       <c r="C4" s="2">
         <v>13</v>
@@ -2697,12 +2696,12 @@
         <v>65</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" t="s">
         <v>41</v>
-      </c>
-      <c r="B5" t="s">
-        <v>42</v>
       </c>
       <c r="C5" s="2">
         <v>7</v>
@@ -2774,12 +2773,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" t="s">
         <v>43</v>
-      </c>
-      <c r="B6" t="s">
-        <v>44</v>
       </c>
       <c r="C6" s="2">
         <v>17</v>
@@ -2881,12 +2880,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" t="s">
         <v>45</v>
-      </c>
-      <c r="B7" t="s">
-        <v>46</v>
       </c>
       <c r="C7" s="2">
         <v>11</v>
@@ -2988,12 +2987,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" t="s">
         <v>47</v>
-      </c>
-      <c r="B8" t="s">
-        <v>48</v>
       </c>
       <c r="C8" s="2">
         <v>11</v>
@@ -3065,12 +3064,12 @@
         <v>65</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B9" t="s">
         <v>49</v>
-      </c>
-      <c r="B9" t="s">
-        <v>50</v>
       </c>
       <c r="C9" s="2">
         <v>6</v>
@@ -3139,12 +3138,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>50</v>
+      </c>
+      <c r="B10" t="s">
         <v>51</v>
-      </c>
-      <c r="B10" t="s">
-        <v>52</v>
       </c>
       <c r="C10" s="2">
         <v>3</v>
@@ -3216,12 +3215,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
+        <v>52</v>
+      </c>
+      <c r="B11" t="s">
         <v>53</v>
-      </c>
-      <c r="B11" t="s">
-        <v>54</v>
       </c>
       <c r="C11" s="2">
         <v>3</v>
@@ -3293,12 +3292,12 @@
         <v>90</v>
       </c>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
+        <v>54</v>
+      </c>
+      <c r="B12" t="s">
         <v>55</v>
-      </c>
-      <c r="B12" t="s">
-        <v>56</v>
       </c>
       <c r="C12" s="2">
         <v>8</v>
@@ -3376,12 +3375,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
+        <v>56</v>
+      </c>
+      <c r="B13" t="s">
         <v>57</v>
-      </c>
-      <c r="B13" t="s">
-        <v>58</v>
       </c>
       <c r="C13" s="2">
         <v>5</v>
@@ -3453,12 +3452,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
+        <v>58</v>
+      </c>
+      <c r="B14" t="s">
         <v>59</v>
-      </c>
-      <c r="B14" t="s">
-        <v>60</v>
       </c>
       <c r="C14" s="2">
         <v>4</v>
@@ -3536,12 +3535,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
+        <v>60</v>
+      </c>
+      <c r="B15" t="s">
         <v>61</v>
-      </c>
-      <c r="B15" t="s">
-        <v>62</v>
       </c>
       <c r="C15" s="2">
         <v>3</v>
@@ -3595,12 +3594,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
+        <v>62</v>
+      </c>
+      <c r="B16" t="s">
         <v>63</v>
-      </c>
-      <c r="B16" t="s">
-        <v>64</v>
       </c>
       <c r="C16" s="2">
         <v>8</v>
@@ -3666,12 +3665,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="17" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
+        <v>64</v>
+      </c>
+      <c r="B17" t="s">
         <v>65</v>
-      </c>
-      <c r="B17" t="s">
-        <v>66</v>
       </c>
       <c r="C17" s="2">
         <v>16</v>
@@ -3761,12 +3760,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="18" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
+        <v>66</v>
+      </c>
+      <c r="B18" t="s">
         <v>67</v>
-      </c>
-      <c r="B18" t="s">
-        <v>68</v>
       </c>
       <c r="C18" s="2">
         <v>8</v>
@@ -3856,12 +3855,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="19" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
+        <v>68</v>
+      </c>
+      <c r="B19" t="s">
         <v>69</v>
-      </c>
-      <c r="B19" t="s">
-        <v>70</v>
       </c>
       <c r="C19" s="2">
         <v>4</v>
@@ -3933,12 +3932,12 @@
         <v>90</v>
       </c>
     </row>
-    <row r="20" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
+        <v>70</v>
+      </c>
+      <c r="B20" t="s">
         <v>71</v>
-      </c>
-      <c r="B20" t="s">
-        <v>72</v>
       </c>
       <c r="C20" s="2">
         <v>2</v>
@@ -4016,12 +4015,12 @@
         <v>90</v>
       </c>
     </row>
-    <row r="21" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
+        <v>72</v>
+      </c>
+      <c r="B21" t="s">
         <v>73</v>
-      </c>
-      <c r="B21" t="s">
-        <v>74</v>
       </c>
       <c r="C21" s="2">
         <v>1</v>
@@ -4102,12 +4101,12 @@
         <v>90</v>
       </c>
     </row>
-    <row r="22" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
+        <v>74</v>
+      </c>
+      <c r="B22" t="s">
         <v>75</v>
-      </c>
-      <c r="B22" t="s">
-        <v>76</v>
       </c>
       <c r="C22" s="2">
         <v>9</v>
@@ -4185,12 +4184,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="23" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
+        <v>76</v>
+      </c>
+      <c r="B23" t="s">
         <v>77</v>
-      </c>
-      <c r="B23" t="s">
-        <v>78</v>
       </c>
       <c r="C23" s="2">
         <v>5</v>
@@ -4268,12 +4267,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="24" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
+        <v>78</v>
+      </c>
+      <c r="B24" t="s">
         <v>79</v>
-      </c>
-      <c r="B24" t="s">
-        <v>80</v>
       </c>
       <c r="C24" s="2">
         <v>15</v>
@@ -4357,12 +4356,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="25" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
+        <v>80</v>
+      </c>
+      <c r="B25" t="s">
         <v>81</v>
-      </c>
-      <c r="B25" t="s">
-        <v>82</v>
       </c>
       <c r="C25" s="2">
         <v>9</v>
@@ -4452,12 +4451,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="26" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
+        <v>82</v>
+      </c>
+      <c r="B26" t="s">
         <v>83</v>
-      </c>
-      <c r="B26" t="s">
-        <v>84</v>
       </c>
       <c r="C26" s="2">
         <v>12</v>
@@ -4535,12 +4534,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="27" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
+        <v>84</v>
+      </c>
+      <c r="B27" t="s">
         <v>85</v>
-      </c>
-      <c r="B27" t="s">
-        <v>86</v>
       </c>
       <c r="C27" s="2">
         <v>4</v>
@@ -4618,12 +4617,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="28" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
+        <v>86</v>
+      </c>
+      <c r="B28" t="s">
         <v>87</v>
-      </c>
-      <c r="B28" t="s">
-        <v>88</v>
       </c>
       <c r="C28" s="2">
         <v>3</v>
@@ -4701,12 +4700,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="29" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
+        <v>88</v>
+      </c>
+      <c r="B29" t="s">
         <v>89</v>
-      </c>
-      <c r="B29" t="s">
-        <v>90</v>
       </c>
       <c r="C29" s="2">
         <v>8</v>
@@ -4778,12 +4777,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="30" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
+        <v>90</v>
+      </c>
+      <c r="B30" t="s">
         <v>91</v>
-      </c>
-      <c r="B30" t="s">
-        <v>92</v>
       </c>
       <c r="C30" s="2">
         <v>6</v>
@@ -4855,12 +4854,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="31" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
+        <v>92</v>
+      </c>
+      <c r="B31" t="s">
         <v>93</v>
-      </c>
-      <c r="B31" t="s">
-        <v>94</v>
       </c>
       <c r="C31" s="2">
         <v>5</v>
@@ -4932,12 +4931,12 @@
         <v>90</v>
       </c>
     </row>
-    <row r="32" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
+        <v>94</v>
+      </c>
+      <c r="B32" t="s">
         <v>95</v>
-      </c>
-      <c r="B32" t="s">
-        <v>96</v>
       </c>
       <c r="C32" s="2">
         <v>6</v>
@@ -5015,12 +5014,12 @@
         <v>90</v>
       </c>
     </row>
-    <row r="33" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
+        <v>96</v>
+      </c>
+      <c r="B33" t="s">
         <v>97</v>
-      </c>
-      <c r="B33" t="s">
-        <v>98</v>
       </c>
       <c r="C33" s="2">
         <v>6</v>
@@ -5092,12 +5091,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="34" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
+        <v>98</v>
+      </c>
+      <c r="B34" t="s">
         <v>99</v>
-      </c>
-      <c r="B34" t="s">
-        <v>100</v>
       </c>
       <c r="C34" s="2">
         <v>8</v>
@@ -5193,12 +5192,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="35" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
+        <v>100</v>
+      </c>
+      <c r="B35" t="s">
         <v>101</v>
-      </c>
-      <c r="B35" t="s">
-        <v>102</v>
       </c>
       <c r="C35" s="2">
         <v>6</v>
@@ -5294,12 +5293,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="36" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
+        <v>102</v>
+      </c>
+      <c r="B36" t="s">
         <v>103</v>
-      </c>
-      <c r="B36" t="s">
-        <v>104</v>
       </c>
       <c r="C36" s="2">
         <v>6</v>
@@ -5359,12 +5358,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="37" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
+        <v>104</v>
+      </c>
+      <c r="B37" t="s">
         <v>105</v>
-      </c>
-      <c r="B37" t="s">
-        <v>106</v>
       </c>
       <c r="C37" s="2">
         <v>7</v>
@@ -5424,12 +5423,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="38" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
+        <v>106</v>
+      </c>
+      <c r="B38" t="s">
         <v>107</v>
-      </c>
-      <c r="B38" t="s">
-        <v>108</v>
       </c>
       <c r="C38" s="2">
         <v>4</v>
@@ -5489,12 +5488,12 @@
         <v>120</v>
       </c>
     </row>
-    <row r="39" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
+        <v>108</v>
+      </c>
+      <c r="B39" t="s">
         <v>109</v>
-      </c>
-      <c r="B39" t="s">
-        <v>110</v>
       </c>
       <c r="C39" s="2">
         <v>19</v>
@@ -5572,12 +5571,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="40" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
+        <v>110</v>
+      </c>
+      <c r="B40" t="s">
         <v>111</v>
-      </c>
-      <c r="B40" t="s">
-        <v>112</v>
       </c>
       <c r="C40" s="2">
         <v>12</v>
@@ -5655,12 +5654,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="41" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
+        <v>112</v>
+      </c>
+      <c r="B41" t="s">
         <v>113</v>
-      </c>
-      <c r="B41" t="s">
-        <v>114</v>
       </c>
       <c r="C41" s="2">
         <v>14</v>
@@ -5744,12 +5743,12 @@
         <v>85</v>
       </c>
     </row>
-    <row r="42" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
+        <v>114</v>
+      </c>
+      <c r="B42" t="s">
         <v>115</v>
-      </c>
-      <c r="B42" t="s">
-        <v>116</v>
       </c>
       <c r="C42" s="2">
         <v>9</v>
@@ -5815,12 +5814,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="43" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
+        <v>116</v>
+      </c>
+      <c r="B43" t="s">
         <v>117</v>
-      </c>
-      <c r="B43" t="s">
-        <v>118</v>
       </c>
       <c r="C43" s="2">
         <v>12</v>
@@ -5898,12 +5897,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="44" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
+        <v>118</v>
+      </c>
+      <c r="B44" t="s">
         <v>119</v>
-      </c>
-      <c r="B44" t="s">
-        <v>120</v>
       </c>
       <c r="C44" s="2">
         <v>5</v>
@@ -5981,12 +5980,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="45" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
+        <v>120</v>
+      </c>
+      <c r="B45" t="s">
         <v>121</v>
-      </c>
-      <c r="B45" t="s">
-        <v>122</v>
       </c>
       <c r="C45" s="2">
         <v>7</v>
@@ -6049,12 +6048,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="46" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
+        <v>122</v>
+      </c>
+      <c r="B46" t="s">
         <v>123</v>
-      </c>
-      <c r="B46" t="s">
-        <v>124</v>
       </c>
       <c r="C46" s="2">
         <v>4</v>
@@ -6126,12 +6125,12 @@
         <v>90</v>
       </c>
     </row>
-    <row r="47" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
+        <v>124</v>
+      </c>
+      <c r="B47" t="s">
         <v>125</v>
-      </c>
-      <c r="B47" t="s">
-        <v>126</v>
       </c>
       <c r="C47" s="2">
         <v>7</v>
@@ -6209,12 +6208,12 @@
         <v>90</v>
       </c>
     </row>
-    <row r="48" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
+        <v>126</v>
+      </c>
+      <c r="B48" t="s">
         <v>127</v>
-      </c>
-      <c r="B48" t="s">
-        <v>128</v>
       </c>
       <c r="C48" s="2">
         <v>5</v>
@@ -6286,12 +6285,12 @@
         <v>90</v>
       </c>
     </row>
-    <row r="49" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
+        <v>128</v>
+      </c>
+      <c r="B49" t="s">
         <v>129</v>
-      </c>
-      <c r="B49" t="s">
-        <v>130</v>
       </c>
       <c r="C49" s="2">
         <v>9</v>
@@ -6369,12 +6368,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="50" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
+        <v>130</v>
+      </c>
+      <c r="B50" t="s">
         <v>131</v>
-      </c>
-      <c r="B50" t="s">
-        <v>132</v>
       </c>
       <c r="C50" s="2">
         <v>4</v>
@@ -6446,12 +6445,12 @@
         <v>90</v>
       </c>
     </row>
-    <row r="51" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
+        <v>132</v>
+      </c>
+      <c r="B51" t="s">
         <v>133</v>
-      </c>
-      <c r="B51" t="s">
-        <v>134</v>
       </c>
       <c r="C51" s="2">
         <v>4</v>
@@ -6523,12 +6522,12 @@
         <v>90</v>
       </c>
     </row>
-    <row r="52" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
+        <v>134</v>
+      </c>
+      <c r="B52" t="s">
         <v>135</v>
-      </c>
-      <c r="B52" t="s">
-        <v>136</v>
       </c>
       <c r="C52" s="2">
         <v>30</v>
@@ -6606,12 +6605,12 @@
         <v>65</v>
       </c>
     </row>
-    <row r="53" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
+        <v>136</v>
+      </c>
+      <c r="B53" t="s">
         <v>137</v>
-      </c>
-      <c r="B53" t="s">
-        <v>138</v>
       </c>
       <c r="C53" s="2">
         <v>17</v>
@@ -6689,12 +6688,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="54" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
+        <v>138</v>
+      </c>
+      <c r="B54" t="s">
         <v>139</v>
-      </c>
-      <c r="B54" t="s">
-        <v>140</v>
       </c>
       <c r="C54" s="2">
         <v>8</v>
@@ -6772,12 +6771,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="55" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
+        <v>140</v>
+      </c>
+      <c r="B55" t="s">
         <v>141</v>
-      </c>
-      <c r="B55" t="s">
-        <v>142</v>
       </c>
       <c r="C55" s="2">
         <v>14</v>
@@ -6855,12 +6854,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="56" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
+        <v>142</v>
+      </c>
+      <c r="B56" t="s">
         <v>143</v>
-      </c>
-      <c r="B56" t="s">
-        <v>144</v>
       </c>
       <c r="C56" s="2">
         <v>8</v>
@@ -6938,12 +6937,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="57" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
+        <v>144</v>
+      </c>
+      <c r="B57" t="s">
         <v>145</v>
-      </c>
-      <c r="B57" t="s">
-        <v>146</v>
       </c>
       <c r="C57" s="2">
         <v>10</v>
@@ -7015,12 +7014,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="58" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
+        <v>146</v>
+      </c>
+      <c r="B58" t="s">
         <v>147</v>
-      </c>
-      <c r="B58" t="s">
-        <v>148</v>
       </c>
       <c r="C58" s="2">
         <v>4</v>
@@ -7080,12 +7079,12 @@
         <v>120</v>
       </c>
     </row>
-    <row r="59" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
+        <v>148</v>
+      </c>
+      <c r="B59" t="s">
         <v>149</v>
-      </c>
-      <c r="B59" t="s">
-        <v>150</v>
       </c>
       <c r="C59" s="2">
         <v>15</v>
@@ -7163,12 +7162,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="60" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
+        <v>150</v>
+      </c>
+      <c r="B60" t="s">
         <v>151</v>
-      </c>
-      <c r="B60" t="s">
-        <v>152</v>
       </c>
       <c r="C60" s="2">
         <v>9</v>
@@ -7246,12 +7245,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="61" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
+        <v>152</v>
+      </c>
+      <c r="B61" t="s">
         <v>153</v>
-      </c>
-      <c r="B61" t="s">
-        <v>154</v>
       </c>
       <c r="C61" s="2">
         <v>7</v>
@@ -7323,12 +7322,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="62" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
+        <v>154</v>
+      </c>
+      <c r="B62" t="s">
         <v>155</v>
-      </c>
-      <c r="B62" t="s">
-        <v>156</v>
       </c>
       <c r="C62" s="2">
         <v>4</v>
@@ -7400,12 +7399,12 @@
         <v>100</v>
       </c>
     </row>
-    <row r="63" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
+        <v>156</v>
+      </c>
+      <c r="B63" t="s">
         <v>157</v>
-      </c>
-      <c r="B63" t="s">
-        <v>158</v>
       </c>
       <c r="C63" s="2">
         <v>2</v>
@@ -7477,12 +7476,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="64" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
+        <v>158</v>
+      </c>
+      <c r="B64" t="s">
         <v>159</v>
-      </c>
-      <c r="B64" t="s">
-        <v>160</v>
       </c>
       <c r="C64" s="2">
         <v>13</v>
@@ -7572,12 +7571,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="65" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
+        <v>160</v>
+      </c>
+      <c r="B65" t="s">
         <v>161</v>
-      </c>
-      <c r="B65" t="s">
-        <v>162</v>
       </c>
       <c r="C65" s="2">
         <v>9</v>
@@ -7661,12 +7660,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="66" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
+        <v>162</v>
+      </c>
+      <c r="B66" t="s">
         <v>163</v>
-      </c>
-      <c r="B66" t="s">
-        <v>164</v>
       </c>
       <c r="C66" s="2">
         <v>7</v>
@@ -7744,12 +7743,12 @@
         <v>90</v>
       </c>
     </row>
-    <row r="67" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
+        <v>164</v>
+      </c>
+      <c r="B67" t="s">
         <v>165</v>
-      </c>
-      <c r="B67" t="s">
-        <v>166</v>
       </c>
       <c r="C67" s="2">
         <v>7</v>
@@ -7827,12 +7826,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="68" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
+        <v>166</v>
+      </c>
+      <c r="B68" t="s">
         <v>167</v>
-      </c>
-      <c r="B68" t="s">
-        <v>168</v>
       </c>
       <c r="C68" s="2">
         <v>8</v>
@@ -7910,12 +7909,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="69" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
+        <v>168</v>
+      </c>
+      <c r="B69" t="s">
         <v>169</v>
-      </c>
-      <c r="B69" t="s">
-        <v>170</v>
       </c>
       <c r="C69" s="2">
         <v>19</v>
@@ -7993,12 +7992,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="70" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
+        <v>170</v>
+      </c>
+      <c r="B70" t="s">
         <v>171</v>
-      </c>
-      <c r="B70" t="s">
-        <v>172</v>
       </c>
       <c r="C70" s="2">
         <v>6</v>
@@ -8097,12 +8096,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="71" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
+        <v>172</v>
+      </c>
+      <c r="B71" t="s">
         <v>173</v>
-      </c>
-      <c r="B71" t="s">
-        <v>174</v>
       </c>
       <c r="C71" s="2">
         <v>7</v>
@@ -8180,12 +8179,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="72" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
+        <v>174</v>
+      </c>
+      <c r="B72" t="s">
         <v>175</v>
-      </c>
-      <c r="B72" t="s">
-        <v>176</v>
       </c>
       <c r="C72" s="2">
         <v>6</v>
@@ -8263,12 +8262,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="73" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
+        <v>176</v>
+      </c>
+      <c r="B73" t="s">
         <v>177</v>
-      </c>
-      <c r="B73" t="s">
-        <v>178</v>
       </c>
       <c r="C73" s="2">
         <v>5</v>
@@ -8346,12 +8345,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="74" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
+        <v>178</v>
+      </c>
+      <c r="B74" t="s">
         <v>179</v>
-      </c>
-      <c r="B74" t="s">
-        <v>180</v>
       </c>
       <c r="C74" s="2">
         <v>4</v>
@@ -8429,12 +8428,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="75" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
+        <v>180</v>
+      </c>
+      <c r="B75" t="s">
         <v>181</v>
-      </c>
-      <c r="B75" t="s">
-        <v>182</v>
       </c>
       <c r="C75" s="2">
         <v>6</v>
@@ -8518,12 +8517,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="76" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
+        <v>182</v>
+      </c>
+      <c r="B76" t="s">
         <v>183</v>
-      </c>
-      <c r="B76" t="s">
-        <v>184</v>
       </c>
       <c r="C76" s="2">
         <v>10</v>
@@ -8616,12 +8615,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="77" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
+        <v>184</v>
+      </c>
+      <c r="B77" t="s">
         <v>185</v>
-      </c>
-      <c r="B77" t="s">
-        <v>186</v>
       </c>
       <c r="C77" s="2">
         <v>6</v>
@@ -8705,12 +8704,12 @@
         <v>100</v>
       </c>
     </row>
-    <row r="78" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
+        <v>186</v>
+      </c>
+      <c r="B78" t="s">
         <v>187</v>
-      </c>
-      <c r="B78" t="s">
-        <v>188</v>
       </c>
       <c r="C78" s="2">
         <v>9</v>
@@ -8803,12 +8802,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="79" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
+        <v>188</v>
+      </c>
+      <c r="B79" t="s">
         <v>189</v>
-      </c>
-      <c r="B79" t="s">
-        <v>190</v>
       </c>
       <c r="C79" s="2">
         <v>7</v>
@@ -8886,12 +8885,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="80" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
+        <v>190</v>
+      </c>
+      <c r="B80" t="s">
         <v>191</v>
-      </c>
-      <c r="B80" t="s">
-        <v>192</v>
       </c>
       <c r="C80" s="2">
         <v>11</v>
@@ -8966,12 +8965,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="81" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
+        <v>192</v>
+      </c>
+      <c r="B81" t="s">
         <v>193</v>
-      </c>
-      <c r="B81" t="s">
-        <v>194</v>
       </c>
       <c r="C81" s="2">
         <v>6</v>
@@ -9043,12 +9042,12 @@
         <v>65</v>
       </c>
     </row>
-    <row r="82" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
+        <v>194</v>
+      </c>
+      <c r="B82" t="s">
         <v>195</v>
-      </c>
-      <c r="B82" t="s">
-        <v>196</v>
       </c>
       <c r="C82" s="2">
         <v>12</v>
@@ -9132,12 +9131,12 @@
         <v>65</v>
       </c>
     </row>
-    <row r="83" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A83" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="B83" s="12" t="s">
         <v>197</v>
-      </c>
-      <c r="B83" s="12" t="s">
-        <v>198</v>
       </c>
       <c r="C83" s="5">
         <v>10</v>
@@ -9223,12 +9222,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="84" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
+        <v>198</v>
+      </c>
+      <c r="B84" t="s">
         <v>199</v>
-      </c>
-      <c r="B84" t="s">
-        <v>200</v>
       </c>
       <c r="C84" s="2">
         <v>0</v>
@@ -9240,12 +9239,12 @@
         <v>237</v>
       </c>
     </row>
-    <row r="85" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
+        <v>200</v>
+      </c>
+      <c r="B85" t="s">
         <v>201</v>
-      </c>
-      <c r="B85" t="s">
-        <v>202</v>
       </c>
       <c r="C85" s="2">
         <v>13</v>
@@ -9323,12 +9322,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="86" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
+        <v>202</v>
+      </c>
+      <c r="B86" t="s">
         <v>203</v>
-      </c>
-      <c r="B86" t="s">
-        <v>204</v>
       </c>
       <c r="C86" s="2">
         <v>7</v>
@@ -9403,12 +9402,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="87" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
+        <v>204</v>
+      </c>
+      <c r="B87" t="s">
         <v>205</v>
-      </c>
-      <c r="B87" t="s">
-        <v>206</v>
       </c>
       <c r="C87" s="2">
         <v>13</v>
@@ -9486,12 +9485,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="88" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
+        <v>206</v>
+      </c>
+      <c r="B88" t="s">
         <v>207</v>
-      </c>
-      <c r="B88" t="s">
-        <v>208</v>
       </c>
       <c r="C88" s="2">
         <v>4</v>
@@ -9569,12 +9568,12 @@
         <v>100</v>
       </c>
     </row>
-    <row r="89" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
+        <v>208</v>
+      </c>
+      <c r="B89" t="s">
         <v>209</v>
-      </c>
-      <c r="B89" t="s">
-        <v>210</v>
       </c>
       <c r="C89" s="2">
         <v>6</v>
@@ -9652,12 +9651,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="90" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
+        <v>210</v>
+      </c>
+      <c r="B90" t="s">
         <v>211</v>
-      </c>
-      <c r="B90" t="s">
-        <v>212</v>
       </c>
       <c r="C90" s="2">
         <v>2</v>
@@ -9735,12 +9734,12 @@
         <v>100</v>
       </c>
     </row>
-    <row r="91" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
+        <v>212</v>
+      </c>
+      <c r="B91" t="s">
         <v>213</v>
-      </c>
-      <c r="B91" t="s">
-        <v>214</v>
       </c>
       <c r="C91" s="2">
         <v>8</v>
@@ -9818,12 +9817,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="92" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
+        <v>214</v>
+      </c>
+      <c r="B92" t="s">
         <v>215</v>
-      </c>
-      <c r="B92" t="s">
-        <v>216</v>
       </c>
       <c r="C92" s="2">
         <v>9</v>
@@ -9907,12 +9906,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="93" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
+        <v>216</v>
+      </c>
+      <c r="B93" t="s">
         <v>217</v>
-      </c>
-      <c r="B93" t="s">
-        <v>218</v>
       </c>
       <c r="C93" s="2">
         <v>4</v>
@@ -9990,12 +9989,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="94" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
+        <v>218</v>
+      </c>
+      <c r="B94" t="s">
         <v>219</v>
-      </c>
-      <c r="B94" t="s">
-        <v>220</v>
       </c>
       <c r="C94" s="2">
         <v>5</v>
@@ -10070,12 +10069,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="95" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
+        <v>220</v>
+      </c>
+      <c r="B95" t="s">
         <v>221</v>
-      </c>
-      <c r="B95" t="s">
-        <v>222</v>
       </c>
       <c r="C95" s="2">
         <v>8</v>
@@ -10147,12 +10146,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="96" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
+        <v>222</v>
+      </c>
+      <c r="B96" t="s">
         <v>223</v>
-      </c>
-      <c r="B96" t="s">
-        <v>224</v>
       </c>
       <c r="C96" s="2">
         <v>3</v>
@@ -10224,12 +10223,12 @@
         <v>90</v>
       </c>
     </row>
-    <row r="97" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
+        <v>224</v>
+      </c>
+      <c r="B97" t="s">
         <v>225</v>
-      </c>
-      <c r="B97" t="s">
-        <v>226</v>
       </c>
       <c r="C97" s="2">
         <v>5</v>
@@ -10307,12 +10306,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="98" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
+        <v>226</v>
+      </c>
+      <c r="B98" t="s">
         <v>227</v>
-      </c>
-      <c r="B98" t="s">
-        <v>228</v>
       </c>
       <c r="C98" s="2">
         <v>5</v>
@@ -10390,12 +10389,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="99" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
+        <v>228</v>
+      </c>
+      <c r="B99" t="s">
         <v>229</v>
-      </c>
-      <c r="B99" t="s">
-        <v>230</v>
       </c>
       <c r="C99" s="2">
         <v>8</v>
@@ -10473,12 +10472,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="100" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
+        <v>230</v>
+      </c>
+      <c r="B100" t="s">
         <v>231</v>
-      </c>
-      <c r="B100" t="s">
-        <v>232</v>
       </c>
       <c r="C100" s="2">
         <v>6</v>
@@ -10562,12 +10561,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="101" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
+        <v>232</v>
+      </c>
+      <c r="B101" t="s">
         <v>233</v>
-      </c>
-      <c r="B101" t="s">
-        <v>234</v>
       </c>
       <c r="C101" s="2">
         <v>3</v>
@@ -10651,12 +10650,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="102" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
+        <v>234</v>
+      </c>
+      <c r="B102" t="s">
         <v>235</v>
-      </c>
-      <c r="B102" t="s">
-        <v>236</v>
       </c>
       <c r="C102" s="2">
         <v>4</v>
@@ -10734,12 +10733,12 @@
         <v>65</v>
       </c>
     </row>
-    <row r="103" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
+        <v>236</v>
+      </c>
+      <c r="B103" t="s">
         <v>237</v>
-      </c>
-      <c r="B103" t="s">
-        <v>238</v>
       </c>
       <c r="C103" s="2">
         <v>2</v>
@@ -10817,12 +10816,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="104" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
+        <v>238</v>
+      </c>
+      <c r="B104" t="s">
         <v>239</v>
-      </c>
-      <c r="B104" t="s">
-        <v>240</v>
       </c>
       <c r="C104" s="2">
         <v>0</v>
@@ -10888,12 +10887,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="105" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
+        <v>240</v>
+      </c>
+      <c r="B105" t="s">
         <v>241</v>
-      </c>
-      <c r="B105" t="s">
-        <v>242</v>
       </c>
       <c r="C105" s="2">
         <v>8</v>
@@ -10971,12 +10970,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="106" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
+        <v>242</v>
+      </c>
+      <c r="B106" t="s">
         <v>243</v>
-      </c>
-      <c r="B106" t="s">
-        <v>244</v>
       </c>
       <c r="C106" s="2">
         <v>1</v>
@@ -11054,12 +11053,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="107" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
+        <v>244</v>
+      </c>
+      <c r="B107" t="s">
         <v>245</v>
-      </c>
-      <c r="B107" t="s">
-        <v>246</v>
       </c>
       <c r="C107" s="2">
         <v>2</v>
@@ -11137,12 +11136,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="108" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
+        <v>246</v>
+      </c>
+      <c r="B108" t="s">
         <v>247</v>
-      </c>
-      <c r="B108" t="s">
-        <v>248</v>
       </c>
       <c r="C108" s="2">
         <v>0</v>
@@ -11202,12 +11201,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="109" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
+        <v>248</v>
+      </c>
+      <c r="B109" t="s">
         <v>249</v>
-      </c>
-      <c r="B109" t="s">
-        <v>250</v>
       </c>
       <c r="C109" s="2">
         <v>0</v>
@@ -11267,12 +11266,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="110" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
+        <v>250</v>
+      </c>
+      <c r="B110" t="s">
         <v>251</v>
-      </c>
-      <c r="B110" t="s">
-        <v>252</v>
       </c>
       <c r="C110" s="2">
         <v>4</v>
@@ -11350,12 +11349,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="111" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
+        <v>252</v>
+      </c>
+      <c r="B111" t="s">
         <v>253</v>
-      </c>
-      <c r="B111" t="s">
-        <v>254</v>
       </c>
       <c r="C111" s="2">
         <v>3</v>
@@ -11433,12 +11432,12 @@
         <v>65</v>
       </c>
     </row>
-    <row r="112" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
+        <v>254</v>
+      </c>
+      <c r="B112" t="s">
         <v>255</v>
-      </c>
-      <c r="B112" t="s">
-        <v>256</v>
       </c>
       <c r="C112" s="2">
         <v>1</v>
@@ -11510,12 +11509,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="113" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
+        <v>256</v>
+      </c>
+      <c r="B113" t="s">
         <v>257</v>
-      </c>
-      <c r="B113" t="s">
-        <v>258</v>
       </c>
       <c r="C113" s="2">
         <v>0</v>
@@ -11575,12 +11574,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="114" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
+        <v>258</v>
+      </c>
+      <c r="B114" t="s">
         <v>259</v>
-      </c>
-      <c r="B114" t="s">
-        <v>260</v>
       </c>
       <c r="C114" s="2">
         <v>2</v>
@@ -11655,12 +11654,12 @@
         <v>90</v>
       </c>
     </row>
-    <row r="115" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
+        <v>260</v>
+      </c>
+      <c r="B115" t="s">
         <v>261</v>
-      </c>
-      <c r="B115" t="s">
-        <v>262</v>
       </c>
       <c r="C115" s="2">
         <v>2</v>
@@ -11738,12 +11737,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="116" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
+        <v>262</v>
+      </c>
+      <c r="B116" t="s">
         <v>263</v>
-      </c>
-      <c r="B116" t="s">
-        <v>264</v>
       </c>
       <c r="C116" s="2">
         <v>0</v>
@@ -11818,12 +11817,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="117" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
+        <v>264</v>
+      </c>
+      <c r="B117" t="s">
         <v>265</v>
-      </c>
-      <c r="B117" t="s">
-        <v>266</v>
       </c>
       <c r="C117" s="2">
         <v>2</v>
@@ -11871,12 +11870,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="118" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
+        <v>266</v>
+      </c>
+      <c r="B118" t="s">
         <v>267</v>
-      </c>
-      <c r="B118" t="s">
-        <v>268</v>
       </c>
       <c r="C118" s="2">
         <v>0</v>
@@ -11915,12 +11914,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="119" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A119" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="B119" s="12" t="s">
         <v>269</v>
-      </c>
-      <c r="B119" s="12" t="s">
-        <v>270</v>
       </c>
       <c r="C119" s="5">
         <v>7</v>
@@ -12004,12 +12003,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="120" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
+        <v>270</v>
+      </c>
+      <c r="B120" t="s">
         <v>271</v>
-      </c>
-      <c r="B120" t="s">
-        <v>272</v>
       </c>
       <c r="C120" s="2">
         <v>1</v>
@@ -12081,12 +12080,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="121" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
+        <v>272</v>
+      </c>
+      <c r="B121" t="s">
         <v>273</v>
-      </c>
-      <c r="B121" t="s">
-        <v>274</v>
       </c>
       <c r="C121" s="2">
         <v>4</v>
@@ -12146,12 +12145,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="122" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
+        <v>274</v>
+      </c>
+      <c r="B122" t="s">
         <v>275</v>
-      </c>
-      <c r="B122" t="s">
-        <v>276</v>
       </c>
       <c r="C122" s="2">
         <v>1</v>
@@ -12211,12 +12210,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="123" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
+        <v>276</v>
+      </c>
+      <c r="B123" t="s">
         <v>277</v>
-      </c>
-      <c r="B123" t="s">
-        <v>278</v>
       </c>
       <c r="C123" s="2">
         <v>0</v>
@@ -12270,12 +12269,12 @@
         <v>90</v>
       </c>
     </row>
-    <row r="124" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
+        <v>278</v>
+      </c>
+      <c r="B124" t="s">
         <v>279</v>
-      </c>
-      <c r="B124" t="s">
-        <v>280</v>
       </c>
       <c r="C124" s="2">
         <v>2</v>
@@ -12335,12 +12334,12 @@
         <v>65</v>
       </c>
     </row>
-    <row r="125" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
+        <v>280</v>
+      </c>
+      <c r="B125" t="s">
         <v>281</v>
-      </c>
-      <c r="B125" t="s">
-        <v>282</v>
       </c>
       <c r="C125" s="2">
         <v>6</v>
@@ -12412,12 +12411,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="126" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
+        <v>282</v>
+      </c>
+      <c r="B126" t="s">
         <v>283</v>
-      </c>
-      <c r="B126" t="s">
-        <v>284</v>
       </c>
       <c r="C126" s="2">
         <v>2</v>
@@ -12495,12 +12494,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="127" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A127" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="B127" s="12" t="s">
         <v>285</v>
-      </c>
-      <c r="B127" s="12" t="s">
-        <v>286</v>
       </c>
       <c r="C127" s="5">
         <v>4</v>
@@ -12574,12 +12573,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="128" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A128" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="B128" s="12" t="s">
         <v>287</v>
-      </c>
-      <c r="B128" s="12" t="s">
-        <v>288</v>
       </c>
       <c r="C128" s="5">
         <v>5</v>
@@ -12653,12 +12652,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="129" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
+        <v>288</v>
+      </c>
+      <c r="B129" t="s">
         <v>289</v>
-      </c>
-      <c r="B129" t="s">
-        <v>290</v>
       </c>
       <c r="C129" s="2">
         <v>0</v>
@@ -12736,12 +12735,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="130" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
+        <v>290</v>
+      </c>
+      <c r="B130" t="s">
         <v>291</v>
-      </c>
-      <c r="B130" t="s">
-        <v>292</v>
       </c>
       <c r="C130" s="2">
         <v>2</v>
@@ -12819,12 +12818,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="131" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
+        <v>292</v>
+      </c>
+      <c r="B131" t="s">
         <v>293</v>
-      </c>
-      <c r="B131" t="s">
-        <v>294</v>
       </c>
       <c r="C131" s="2">
         <v>1</v>
@@ -12902,12 +12901,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="132" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
+        <v>294</v>
+      </c>
+      <c r="B132" t="s">
         <v>295</v>
-      </c>
-      <c r="B132" t="s">
-        <v>296</v>
       </c>
       <c r="C132" s="2">
         <v>1</v>
@@ -12985,12 +12984,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="133" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
+        <v>296</v>
+      </c>
+      <c r="B133" t="s">
         <v>297</v>
-      </c>
-      <c r="B133" t="s">
-        <v>298</v>
       </c>
       <c r="C133" s="2">
         <v>2</v>
@@ -13068,12 +13067,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="134" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
+        <v>298</v>
+      </c>
+      <c r="B134" t="s">
         <v>299</v>
-      </c>
-      <c r="B134" t="s">
-        <v>300</v>
       </c>
       <c r="C134" s="2">
         <v>9</v>
@@ -13151,12 +13150,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="135" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
+        <v>300</v>
+      </c>
+      <c r="B135" t="s">
         <v>301</v>
-      </c>
-      <c r="B135" t="s">
-        <v>302</v>
       </c>
       <c r="C135" s="2">
         <v>2</v>
@@ -13228,12 +13227,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="136" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
+        <v>302</v>
+      </c>
+      <c r="B136" t="s">
         <v>303</v>
-      </c>
-      <c r="B136" t="s">
-        <v>304</v>
       </c>
       <c r="C136" s="2">
         <v>2</v>
@@ -13311,12 +13310,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="137" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
+        <v>304</v>
+      </c>
+      <c r="B137" t="s">
         <v>305</v>
-      </c>
-      <c r="B137" t="s">
-        <v>306</v>
       </c>
       <c r="C137" s="2">
         <v>2</v>
@@ -13394,12 +13393,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="138" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
+        <v>306</v>
+      </c>
+      <c r="B138" t="s">
         <v>307</v>
-      </c>
-      <c r="B138" t="s">
-        <v>308</v>
       </c>
       <c r="C138" s="2">
         <v>3</v>
@@ -13477,12 +13476,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="139" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
+        <v>308</v>
+      </c>
+      <c r="B139" t="s">
         <v>309</v>
-      </c>
-      <c r="B139" t="s">
-        <v>310</v>
       </c>
       <c r="C139" s="2">
         <v>2</v>
@@ -13560,12 +13559,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="140" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
+        <v>310</v>
+      </c>
+      <c r="B140" t="s">
         <v>311</v>
-      </c>
-      <c r="B140" t="s">
-        <v>312</v>
       </c>
       <c r="C140" s="2">
         <v>5</v>
@@ -13649,12 +13648,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="141" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
+        <v>312</v>
+      </c>
+      <c r="B141" t="s">
         <v>313</v>
-      </c>
-      <c r="B141" t="s">
-        <v>314</v>
       </c>
       <c r="C141" s="2">
         <v>2</v>
@@ -13738,12 +13737,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="142" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
+        <v>314</v>
+      </c>
+      <c r="B142" t="s">
         <v>315</v>
-      </c>
-      <c r="B142" t="s">
-        <v>316</v>
       </c>
       <c r="C142" s="2">
         <v>8</v>
@@ -13821,12 +13820,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="143" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
+        <v>316</v>
+      </c>
+      <c r="B143" t="s">
         <v>317</v>
-      </c>
-      <c r="B143" t="s">
-        <v>318</v>
       </c>
       <c r="C143" s="2">
         <v>8</v>
@@ -13904,12 +13903,12 @@
         <v>90</v>
       </c>
     </row>
-    <row r="144" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
+        <v>318</v>
+      </c>
+      <c r="B144" t="s">
         <v>319</v>
-      </c>
-      <c r="B144" t="s">
-        <v>320</v>
       </c>
       <c r="C144" s="2">
         <v>6</v>
@@ -13987,12 +13986,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="145" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A145" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="B145" s="12" t="s">
         <v>321</v>
-      </c>
-      <c r="B145" s="12" t="s">
-        <v>322</v>
       </c>
       <c r="C145" s="5">
         <v>2</v>
@@ -14064,12 +14063,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="146" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
+        <v>322</v>
+      </c>
+      <c r="B146" t="s">
         <v>323</v>
-      </c>
-      <c r="B146" t="s">
-        <v>324</v>
       </c>
       <c r="C146" s="2">
         <v>0</v>
@@ -14147,12 +14146,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="147" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
+        <v>324</v>
+      </c>
+      <c r="B147" t="s">
         <v>325</v>
-      </c>
-      <c r="B147" t="s">
-        <v>326</v>
       </c>
       <c r="C147" s="2">
         <v>3</v>
@@ -14230,12 +14229,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="148" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
+        <v>326</v>
+      </c>
+      <c r="B148" t="s">
         <v>327</v>
-      </c>
-      <c r="B148" t="s">
-        <v>328</v>
       </c>
       <c r="C148" s="2">
         <v>0</v>
@@ -14292,12 +14291,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="149" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
+        <v>328</v>
+      </c>
+      <c r="B149" t="s">
         <v>329</v>
-      </c>
-      <c r="B149" t="s">
-        <v>330</v>
       </c>
       <c r="C149" s="2">
         <v>0</v>
@@ -14354,12 +14353,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="150" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
+        <v>330</v>
+      </c>
+      <c r="B150" t="s">
         <v>331</v>
-      </c>
-      <c r="B150" t="s">
-        <v>332</v>
       </c>
       <c r="C150" s="2">
         <v>0</v>
@@ -14407,12 +14406,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="151" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
+        <v>332</v>
+      </c>
+      <c r="B151" t="s">
         <v>333</v>
-      </c>
-      <c r="B151" t="s">
-        <v>334</v>
       </c>
       <c r="C151" s="2">
         <v>0</v>
@@ -14487,12 +14486,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="152" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
+        <v>334</v>
+      </c>
+      <c r="B152" t="s">
         <v>335</v>
-      </c>
-      <c r="B152" t="s">
-        <v>336</v>
       </c>
       <c r="C152" s="2">
         <v>1</v>
@@ -14552,12 +14551,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="153" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
+        <v>336</v>
+      </c>
+      <c r="B153" t="s">
         <v>337</v>
-      </c>
-      <c r="B153" t="s">
-        <v>338</v>
       </c>
       <c r="C153" s="2">
         <v>1</v>
@@ -14617,12 +14616,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="154" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
+        <v>338</v>
+      </c>
+      <c r="B154" t="s">
         <v>339</v>
-      </c>
-      <c r="B154" t="s">
-        <v>340</v>
       </c>
       <c r="C154" s="2">
         <v>0</v>
@@ -14706,12 +14705,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="155" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
+        <v>340</v>
+      </c>
+      <c r="B155" t="s">
         <v>341</v>
-      </c>
-      <c r="B155" t="s">
-        <v>342</v>
       </c>
       <c r="C155" s="2">
         <v>1</v>
@@ -14801,12 +14800,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="156" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
+        <v>342</v>
+      </c>
+      <c r="B156" t="s">
         <v>343</v>
-      </c>
-      <c r="B156" t="s">
-        <v>344</v>
       </c>
       <c r="C156" s="2">
         <v>7</v>
@@ -14854,12 +14853,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="157" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
+        <v>344</v>
+      </c>
+      <c r="B157" t="s">
         <v>345</v>
-      </c>
-      <c r="B157" t="s">
-        <v>346</v>
       </c>
       <c r="C157" s="2">
         <v>0</v>
@@ -14916,12 +14915,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="158" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
+        <v>346</v>
+      </c>
+      <c r="B158" t="s">
         <v>347</v>
-      </c>
-      <c r="B158" t="s">
-        <v>348</v>
       </c>
       <c r="C158" s="2">
         <v>0</v>
@@ -14978,12 +14977,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="159" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
+        <v>348</v>
+      </c>
+      <c r="B159" t="s">
         <v>349</v>
-      </c>
-      <c r="B159" t="s">
-        <v>350</v>
       </c>
       <c r="C159" s="2">
         <v>1</v>
@@ -15046,12 +15045,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="160" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
+        <v>350</v>
+      </c>
+      <c r="B160" t="s">
         <v>351</v>
-      </c>
-      <c r="B160" t="s">
-        <v>352</v>
       </c>
       <c r="C160" s="2">
         <v>1</v>
@@ -15114,12 +15113,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="161" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
+        <v>352</v>
+      </c>
+      <c r="B161" t="s">
         <v>353</v>
-      </c>
-      <c r="B161" t="s">
-        <v>354</v>
       </c>
       <c r="C161" s="2">
         <v>1</v>
@@ -15188,12 +15187,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="162" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
+        <v>354</v>
+      </c>
+      <c r="B162" t="s">
         <v>355</v>
-      </c>
-      <c r="B162" t="s">
-        <v>356</v>
       </c>
       <c r="C162" s="2">
         <v>0</v>
@@ -15265,12 +15264,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="163" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
+        <v>356</v>
+      </c>
+      <c r="B163" t="s">
         <v>357</v>
-      </c>
-      <c r="B163" t="s">
-        <v>358</v>
       </c>
       <c r="C163" s="2">
         <v>0</v>
@@ -15336,12 +15335,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="164" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
+        <v>358</v>
+      </c>
+      <c r="B164" t="s">
         <v>359</v>
-      </c>
-      <c r="B164" t="s">
-        <v>360</v>
       </c>
       <c r="C164" s="2">
         <v>0</v>
@@ -15404,12 +15403,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="165" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
+        <v>360</v>
+      </c>
+      <c r="B165" t="s">
         <v>361</v>
-      </c>
-      <c r="B165" t="s">
-        <v>362</v>
       </c>
       <c r="C165" s="2">
         <v>0</v>
@@ -15472,12 +15471,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="166" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
+        <v>362</v>
+      </c>
+      <c r="B166" t="s">
         <v>363</v>
-      </c>
-      <c r="B166" t="s">
-        <v>364</v>
       </c>
       <c r="C166" s="2">
         <v>0</v>
@@ -15561,12 +15560,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="167" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
+        <v>364</v>
+      </c>
+      <c r="B167" t="s">
         <v>365</v>
-      </c>
-      <c r="B167" t="s">
-        <v>366</v>
       </c>
       <c r="C167" s="2">
         <v>0</v>
@@ -15650,12 +15649,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="168" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
+        <v>366</v>
+      </c>
+      <c r="B168" t="s">
         <v>367</v>
-      </c>
-      <c r="B168" t="s">
-        <v>368</v>
       </c>
       <c r="C168" s="2">
         <v>0</v>
@@ -15721,12 +15720,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="169" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
+        <v>368</v>
+      </c>
+      <c r="B169" t="s">
         <v>369</v>
-      </c>
-      <c r="B169" t="s">
-        <v>370</v>
       </c>
       <c r="C169" s="2">
         <v>0</v>
@@ -15810,12 +15809,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="170" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
+        <v>370</v>
+      </c>
+      <c r="B170" t="s">
         <v>371</v>
-      </c>
-      <c r="B170" t="s">
-        <v>372</v>
       </c>
       <c r="C170" s="2">
         <v>0</v>
@@ -15890,12 +15889,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="171" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
+        <v>372</v>
+      </c>
+      <c r="B171" t="s">
         <v>373</v>
-      </c>
-      <c r="B171" t="s">
-        <v>374</v>
       </c>
       <c r="C171" s="2">
         <v>0</v>
@@ -15979,12 +15978,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="172" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
+        <v>374</v>
+      </c>
+      <c r="B172" t="s">
         <v>375</v>
-      </c>
-      <c r="B172" t="s">
-        <v>376</v>
       </c>
       <c r="C172" s="2">
         <v>0</v>
@@ -16038,12 +16037,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="173" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
+        <v>376</v>
+      </c>
+      <c r="B173" t="s">
         <v>377</v>
-      </c>
-      <c r="B173" t="s">
-        <v>378</v>
       </c>
       <c r="C173" s="2">
         <v>0</v>
@@ -16127,12 +16126,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="174" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
+        <v>378</v>
+      </c>
+      <c r="B174" t="s">
         <v>379</v>
-      </c>
-      <c r="B174" t="s">
-        <v>380</v>
       </c>
       <c r="C174" s="2">
         <v>0</v>
@@ -16216,12 +16215,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="175" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
+        <v>380</v>
+      </c>
+      <c r="B175" t="s">
         <v>381</v>
-      </c>
-      <c r="B175" t="s">
-        <v>382</v>
       </c>
       <c r="C175" s="2">
         <v>1</v>
@@ -16278,12 +16277,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="176" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
+        <v>382</v>
+      </c>
+      <c r="B176" t="s">
         <v>383</v>
-      </c>
-      <c r="B176" t="s">
-        <v>384</v>
       </c>
       <c r="C176" s="2">
         <v>1</v>
@@ -16343,12 +16342,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="177" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
+        <v>384</v>
+      </c>
+      <c r="B177" t="s">
         <v>385</v>
-      </c>
-      <c r="B177" t="s">
-        <v>386</v>
       </c>
       <c r="C177" s="2">
         <v>1</v>
@@ -16426,12 +16425,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="178" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
+        <v>386</v>
+      </c>
+      <c r="B178" t="s">
         <v>387</v>
-      </c>
-      <c r="B178" t="s">
-        <v>388</v>
       </c>
       <c r="C178" s="2">
         <v>0</v>
@@ -16503,12 +16502,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="179" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
+        <v>388</v>
+      </c>
+      <c r="B179" t="s">
         <v>389</v>
-      </c>
-      <c r="B179" t="s">
-        <v>390</v>
       </c>
       <c r="C179" s="2">
         <v>7</v>
@@ -16556,12 +16555,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="180" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
+        <v>390</v>
+      </c>
+      <c r="B180" t="s">
         <v>391</v>
-      </c>
-      <c r="B180" t="s">
-        <v>392</v>
       </c>
       <c r="C180" s="2">
         <v>0</v>
@@ -16639,12 +16638,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="181" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
+        <v>392</v>
+      </c>
+      <c r="B181" t="s">
         <v>393</v>
-      </c>
-      <c r="B181" t="s">
-        <v>394</v>
       </c>
       <c r="C181" s="2">
         <v>0</v>
@@ -16722,12 +16721,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="182" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
+        <v>394</v>
+      </c>
+      <c r="B182" t="s">
         <v>395</v>
-      </c>
-      <c r="B182" t="s">
-        <v>396</v>
       </c>
       <c r="C182" s="2">
         <v>0</v>
@@ -16805,12 +16804,12 @@
         <v>90</v>
       </c>
     </row>
-    <row r="183" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
+        <v>396</v>
+      </c>
+      <c r="B183" t="s">
         <v>397</v>
-      </c>
-      <c r="B183" t="s">
-        <v>398</v>
       </c>
       <c r="C183" s="2">
         <v>0</v>
@@ -16888,12 +16887,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="184" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
+        <v>398</v>
+      </c>
+      <c r="B184" t="s">
         <v>399</v>
-      </c>
-      <c r="B184" t="s">
-        <v>400</v>
       </c>
       <c r="C184" s="2">
         <v>0</v>
@@ -16977,12 +16976,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="185" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
+        <v>400</v>
+      </c>
+      <c r="B185" t="s">
         <v>401</v>
-      </c>
-      <c r="B185" t="s">
-        <v>402</v>
       </c>
       <c r="C185" s="2">
         <v>0</v>
@@ -17066,12 +17065,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="186" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
+        <v>402</v>
+      </c>
+      <c r="B186" t="s">
         <v>403</v>
-      </c>
-      <c r="B186" t="s">
-        <v>404</v>
       </c>
       <c r="C186" s="2">
         <v>5</v>
@@ -17155,12 +17154,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="187" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
+        <v>404</v>
+      </c>
+      <c r="B187" t="s">
         <v>405</v>
-      </c>
-      <c r="B187" t="s">
-        <v>406</v>
       </c>
       <c r="C187" s="2">
         <v>1</v>
@@ -17220,12 +17219,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="188" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
+        <v>406</v>
+      </c>
+      <c r="B188" t="s">
         <v>407</v>
-      </c>
-      <c r="B188" t="s">
-        <v>408</v>
       </c>
       <c r="C188" s="2">
         <v>1</v>
@@ -17273,12 +17272,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="189" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
+        <v>408</v>
+      </c>
+      <c r="B189" t="s">
         <v>409</v>
-      </c>
-      <c r="B189" t="s">
-        <v>410</v>
       </c>
       <c r="C189" s="2">
         <v>1</v>
@@ -17326,12 +17325,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="190" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
+        <v>410</v>
+      </c>
+      <c r="B190" t="s">
         <v>411</v>
-      </c>
-      <c r="B190" t="s">
-        <v>412</v>
       </c>
       <c r="C190" s="2">
         <v>1</v>
@@ -17379,12 +17378,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="191" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
+        <v>412</v>
+      </c>
+      <c r="B191" t="s">
         <v>413</v>
-      </c>
-      <c r="B191" t="s">
-        <v>414</v>
       </c>
       <c r="C191" s="2">
         <v>0</v>
@@ -17444,12 +17443,12 @@
         <v>55</v>
       </c>
     </row>
-    <row r="192" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
+        <v>414</v>
+      </c>
+      <c r="B192" t="s">
         <v>415</v>
-      </c>
-      <c r="B192" t="s">
-        <v>416</v>
       </c>
       <c r="C192" s="2">
         <v>1</v>
@@ -17506,12 +17505,12 @@
         <v>55</v>
       </c>
     </row>
-    <row r="193" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
+        <v>416</v>
+      </c>
+      <c r="B193" t="s">
         <v>417</v>
-      </c>
-      <c r="B193" t="s">
-        <v>418</v>
       </c>
       <c r="C193" s="2">
         <v>3</v>
@@ -17595,12 +17594,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="194" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
+        <v>418</v>
+      </c>
+      <c r="B194" t="s">
         <v>419</v>
-      </c>
-      <c r="B194" t="s">
-        <v>420</v>
       </c>
       <c r="C194" s="2">
         <v>1</v>
@@ -17651,12 +17650,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="195" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
+        <v>420</v>
+      </c>
+      <c r="B195" t="s">
         <v>421</v>
-      </c>
-      <c r="B195" t="s">
-        <v>422</v>
       </c>
       <c r="C195" s="2">
         <v>1</v>
@@ -17728,12 +17727,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="196" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
+        <v>422</v>
+      </c>
+      <c r="B196" t="s">
         <v>423</v>
-      </c>
-      <c r="B196" t="s">
-        <v>424</v>
       </c>
       <c r="C196" s="2">
         <v>0</v>
@@ -17784,12 +17783,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="197" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
+        <v>424</v>
+      </c>
+      <c r="B197" t="s">
         <v>425</v>
-      </c>
-      <c r="B197" t="s">
-        <v>426</v>
       </c>
       <c r="C197" s="2">
         <v>0</v>
@@ -17855,12 +17854,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="198" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
+        <v>426</v>
+      </c>
+      <c r="B198" t="s">
         <v>427</v>
-      </c>
-      <c r="B198" t="s">
-        <v>428</v>
       </c>
       <c r="C198" s="2">
         <v>0</v>
@@ -17923,12 +17922,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="199" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
+        <v>428</v>
+      </c>
+      <c r="B199" t="s">
         <v>429</v>
-      </c>
-      <c r="B199" t="s">
-        <v>430</v>
       </c>
       <c r="C199" s="2">
         <v>0</v>
@@ -18024,12 +18023,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="200" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
+        <v>430</v>
+      </c>
+      <c r="B200" t="s">
         <v>431</v>
-      </c>
-      <c r="B200" t="s">
-        <v>432</v>
       </c>
       <c r="C200" s="2">
         <v>0</v>
@@ -18071,12 +18070,12 @@
         <v>100</v>
       </c>
     </row>
-    <row r="201" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
+        <v>432</v>
+      </c>
+      <c r="B201" t="s">
         <v>433</v>
-      </c>
-      <c r="B201" t="s">
-        <v>434</v>
       </c>
       <c r="C201" s="2">
         <v>1</v>
@@ -18178,12 +18177,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="202" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
+        <v>434</v>
+      </c>
+      <c r="B202" t="s">
         <v>435</v>
-      </c>
-      <c r="B202" t="s">
-        <v>436</v>
       </c>
       <c r="C202" s="2">
         <v>3</v>
@@ -18261,12 +18260,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="203" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
+        <v>436</v>
+      </c>
+      <c r="B203" t="s">
         <v>437</v>
-      </c>
-      <c r="B203" t="s">
-        <v>438</v>
       </c>
       <c r="C203" s="2">
         <v>0</v>
@@ -18344,12 +18343,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="204" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
+        <v>438</v>
+      </c>
+      <c r="B204" t="s">
         <v>439</v>
-      </c>
-      <c r="B204" t="s">
-        <v>440</v>
       </c>
       <c r="C204" s="2">
         <v>0</v>
@@ -18427,12 +18426,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="205" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
+        <v>440</v>
+      </c>
+      <c r="B205" t="s">
         <v>441</v>
-      </c>
-      <c r="B205" t="s">
-        <v>442</v>
       </c>
       <c r="C205" s="2">
         <v>0</v>
@@ -18510,12 +18509,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="206" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
+        <v>442</v>
+      </c>
+      <c r="B206" t="s">
         <v>443</v>
-      </c>
-      <c r="B206" t="s">
-        <v>444</v>
       </c>
       <c r="C206" s="2">
         <v>0</v>
@@ -18572,12 +18571,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="207" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
+        <v>444</v>
+      </c>
+      <c r="B207" t="s">
         <v>445</v>
-      </c>
-      <c r="B207" t="s">
-        <v>446</v>
       </c>
       <c r="C207" s="2">
         <v>1</v>
@@ -18634,12 +18633,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="208" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
+        <v>446</v>
+      </c>
+      <c r="B208" t="s">
         <v>447</v>
-      </c>
-      <c r="B208" t="s">
-        <v>448</v>
       </c>
       <c r="C208" s="2">
         <v>1</v>
@@ -18714,12 +18713,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="209" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
+        <v>448</v>
+      </c>
+      <c r="B209" t="s">
         <v>449</v>
-      </c>
-      <c r="B209" t="s">
-        <v>450</v>
       </c>
       <c r="C209" s="2">
         <v>0</v>
@@ -18785,12 +18784,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="210" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
+        <v>450</v>
+      </c>
+      <c r="B210" t="s">
         <v>451</v>
-      </c>
-      <c r="B210" t="s">
-        <v>452</v>
       </c>
       <c r="C210" s="2">
         <v>2</v>
@@ -18859,12 +18858,12 @@
         <v>65</v>
       </c>
     </row>
-    <row r="211" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
+        <v>452</v>
+      </c>
+      <c r="B211" t="s">
         <v>453</v>
-      </c>
-      <c r="B211" t="s">
-        <v>454</v>
       </c>
       <c r="C211" s="2">
         <v>1</v>
@@ -18966,12 +18965,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="212" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
+        <v>454</v>
+      </c>
+      <c r="B212" t="s">
         <v>455</v>
-      </c>
-      <c r="B212" t="s">
-        <v>456</v>
       </c>
       <c r="C212" s="2">
         <v>1</v>
@@ -19073,12 +19072,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="213" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
+        <v>456</v>
+      </c>
+      <c r="B213" t="s">
         <v>457</v>
-      </c>
-      <c r="B213" t="s">
-        <v>458</v>
       </c>
       <c r="C213" s="2">
         <v>1</v>
@@ -19180,23 +19179,23 @@
         <v>70</v>
       </c>
     </row>
-    <row r="222" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A222" s="13"/>
       <c r="B222" s="14" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="223" spans="1:35" x14ac:dyDescent="0.25">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="223" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A223" s="13" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B223" s="14">
         <v>1200</v>
       </c>
     </row>
-    <row r="224" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A224" s="13" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B224" s="14">
         <v>1000</v>
@@ -19212,7 +19211,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -19221,7 +19220,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/grade.xlsx
+++ b/grade.xlsx
@@ -1316,9 +1316,6 @@
     <t>LcSiMn</t>
   </si>
   <si>
-    <t>Dolvi grades</t>
-  </si>
-  <si>
     <t>c_min</t>
   </si>
   <si>
@@ -1467,6 +1464,9 @@
   </si>
   <si>
     <t>mn_blow_end</t>
+  </si>
+  <si>
+    <t>dolvi grade</t>
   </si>
 </sst>
 </file>
@@ -2464,7 +2464,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>430</v>
+        <v>480</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>1</v>
@@ -2476,139 +2476,139 @@
         <v>3</v>
       </c>
       <c r="F1" s="13" t="s">
+        <v>430</v>
+      </c>
+      <c r="G1" s="13" t="s">
         <v>431</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="H1" s="13" t="s">
         <v>432</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="I1" s="13" t="s">
+        <v>442</v>
+      </c>
+      <c r="J1" s="13" t="s">
+        <v>443</v>
+      </c>
+      <c r="K1" s="13" t="s">
+        <v>444</v>
+      </c>
+      <c r="L1" s="13" t="s">
+        <v>436</v>
+      </c>
+      <c r="M1" s="13" t="s">
+        <v>437</v>
+      </c>
+      <c r="N1" s="13" t="s">
+        <v>438</v>
+      </c>
+      <c r="O1" s="13" t="s">
+        <v>439</v>
+      </c>
+      <c r="P1" s="13" t="s">
+        <v>440</v>
+      </c>
+      <c r="Q1" s="13" t="s">
+        <v>441</v>
+      </c>
+      <c r="R1" s="13" t="s">
         <v>433</v>
       </c>
-      <c r="I1" s="13" t="s">
-        <v>443</v>
-      </c>
-      <c r="J1" s="13" t="s">
-        <v>444</v>
-      </c>
-      <c r="K1" s="13" t="s">
+      <c r="S1" s="13" t="s">
+        <v>434</v>
+      </c>
+      <c r="T1" s="13" t="s">
+        <v>435</v>
+      </c>
+      <c r="U1" s="15" t="s">
+        <v>451</v>
+      </c>
+      <c r="V1" s="15" t="s">
+        <v>452</v>
+      </c>
+      <c r="W1" s="17" t="s">
+        <v>453</v>
+      </c>
+      <c r="X1" s="15" t="s">
+        <v>457</v>
+      </c>
+      <c r="Y1" s="15" t="s">
+        <v>458</v>
+      </c>
+      <c r="Z1" s="15" t="s">
+        <v>459</v>
+      </c>
+      <c r="AA1" s="15" t="s">
+        <v>454</v>
+      </c>
+      <c r="AB1" s="15" t="s">
+        <v>455</v>
+      </c>
+      <c r="AC1" s="17" t="s">
+        <v>456</v>
+      </c>
+      <c r="AD1" s="15" t="s">
+        <v>460</v>
+      </c>
+      <c r="AE1" s="15" t="s">
+        <v>461</v>
+      </c>
+      <c r="AF1" s="15" t="s">
+        <v>462</v>
+      </c>
+      <c r="AG1" s="15" t="s">
+        <v>466</v>
+      </c>
+      <c r="AH1" s="15" t="s">
+        <v>467</v>
+      </c>
+      <c r="AI1" s="15" t="s">
+        <v>468</v>
+      </c>
+      <c r="AJ1" s="15" t="s">
+        <v>472</v>
+      </c>
+      <c r="AK1" s="15" t="s">
+        <v>473</v>
+      </c>
+      <c r="AL1" s="15" t="s">
+        <v>474</v>
+      </c>
+      <c r="AM1" s="15" t="s">
+        <v>463</v>
+      </c>
+      <c r="AN1" s="15" t="s">
+        <v>464</v>
+      </c>
+      <c r="AO1" s="15" t="s">
+        <v>465</v>
+      </c>
+      <c r="AP1" s="15" t="s">
+        <v>469</v>
+      </c>
+      <c r="AQ1" s="15" t="s">
+        <v>470</v>
+      </c>
+      <c r="AR1" s="15" t="s">
+        <v>471</v>
+      </c>
+      <c r="AS1" s="13" t="s">
         <v>445</v>
       </c>
-      <c r="L1" s="13" t="s">
-        <v>437</v>
-      </c>
-      <c r="M1" s="13" t="s">
-        <v>438</v>
-      </c>
-      <c r="N1" s="13" t="s">
-        <v>439</v>
-      </c>
-      <c r="O1" s="13" t="s">
-        <v>440</v>
-      </c>
-      <c r="P1" s="13" t="s">
-        <v>441</v>
-      </c>
-      <c r="Q1" s="13" t="s">
-        <v>442</v>
-      </c>
-      <c r="R1" s="13" t="s">
-        <v>434</v>
-      </c>
-      <c r="S1" s="13" t="s">
-        <v>435</v>
-      </c>
-      <c r="T1" s="13" t="s">
-        <v>436</v>
-      </c>
-      <c r="U1" s="15" t="s">
-        <v>452</v>
-      </c>
-      <c r="V1" s="15" t="s">
-        <v>453</v>
-      </c>
-      <c r="W1" s="17" t="s">
-        <v>454</v>
-      </c>
-      <c r="X1" s="15" t="s">
-        <v>458</v>
-      </c>
-      <c r="Y1" s="15" t="s">
-        <v>459</v>
-      </c>
-      <c r="Z1" s="15" t="s">
-        <v>460</v>
-      </c>
-      <c r="AA1" s="15" t="s">
-        <v>455</v>
-      </c>
-      <c r="AB1" s="15" t="s">
-        <v>456</v>
-      </c>
-      <c r="AC1" s="17" t="s">
-        <v>457</v>
-      </c>
-      <c r="AD1" s="15" t="s">
-        <v>461</v>
-      </c>
-      <c r="AE1" s="15" t="s">
-        <v>462</v>
-      </c>
-      <c r="AF1" s="15" t="s">
-        <v>463</v>
-      </c>
-      <c r="AG1" s="15" t="s">
-        <v>467</v>
-      </c>
-      <c r="AH1" s="15" t="s">
-        <v>468</v>
-      </c>
-      <c r="AI1" s="15" t="s">
-        <v>469</v>
-      </c>
-      <c r="AJ1" s="15" t="s">
-        <v>473</v>
-      </c>
-      <c r="AK1" s="15" t="s">
-        <v>474</v>
-      </c>
-      <c r="AL1" s="15" t="s">
-        <v>475</v>
-      </c>
-      <c r="AM1" s="15" t="s">
-        <v>464</v>
-      </c>
-      <c r="AN1" s="15" t="s">
-        <v>465</v>
-      </c>
-      <c r="AO1" s="15" t="s">
-        <v>466</v>
-      </c>
-      <c r="AP1" s="15" t="s">
-        <v>470</v>
-      </c>
-      <c r="AQ1" s="15" t="s">
-        <v>471</v>
-      </c>
-      <c r="AR1" s="15" t="s">
-        <v>472</v>
-      </c>
-      <c r="AS1" s="13" t="s">
+      <c r="AT1" s="13" t="s">
         <v>446</v>
       </c>
-      <c r="AT1" s="13" t="s">
+      <c r="AU1" s="14" t="s">
         <v>447</v>
       </c>
-      <c r="AU1" s="14" t="s">
+      <c r="AV1" s="15" t="s">
         <v>448</v>
       </c>
-      <c r="AV1" s="15" t="s">
+      <c r="AW1" s="15" t="s">
         <v>449</v>
       </c>
-      <c r="AW1" s="15" t="s">
+      <c r="AX1" s="16" t="s">
         <v>450</v>
-      </c>
-      <c r="AX1" s="16" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="2" spans="1:50" x14ac:dyDescent="0.2">
@@ -31430,154 +31430,154 @@
   <sheetData>
     <row r="1" spans="1:50" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
+        <v>430</v>
+      </c>
+      <c r="B1" s="13" t="s">
         <v>431</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="C1" s="13" t="s">
         <v>432</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="D1" s="13" t="s">
         <v>433</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="E1" s="13" t="s">
         <v>434</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="F1" s="13" t="s">
         <v>435</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="G1" s="13" t="s">
         <v>436</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="H1" s="13" t="s">
         <v>437</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="I1" s="13" t="s">
         <v>438</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="J1" s="13" t="s">
         <v>439</v>
       </c>
-      <c r="J1" s="13" t="s">
+      <c r="K1" s="13" t="s">
         <v>440</v>
       </c>
-      <c r="K1" s="13" t="s">
+      <c r="L1" s="13" t="s">
         <v>441</v>
       </c>
-      <c r="L1" s="13" t="s">
+      <c r="M1" s="13" t="s">
         <v>442</v>
       </c>
-      <c r="M1" s="13" t="s">
+      <c r="N1" s="13" t="s">
         <v>443</v>
       </c>
-      <c r="N1" s="13" t="s">
+      <c r="O1" s="13" t="s">
         <v>444</v>
       </c>
-      <c r="O1" s="13" t="s">
+      <c r="P1" s="13" t="s">
         <v>445</v>
       </c>
-      <c r="P1" s="13" t="s">
+      <c r="Q1" s="13" t="s">
         <v>446</v>
       </c>
-      <c r="Q1" s="13" t="s">
+      <c r="R1" s="14" t="s">
         <v>447</v>
       </c>
-      <c r="R1" s="14" t="s">
+      <c r="S1" s="15" t="s">
         <v>448</v>
       </c>
-      <c r="S1" s="15" t="s">
+      <c r="T1" s="15" t="s">
         <v>449</v>
       </c>
-      <c r="T1" s="15" t="s">
+      <c r="U1" s="16" t="s">
         <v>450</v>
       </c>
-      <c r="U1" s="16" t="s">
+      <c r="V1" s="15" t="s">
         <v>451</v>
       </c>
-      <c r="V1" s="15" t="s">
+      <c r="W1" s="15" t="s">
         <v>452</v>
       </c>
-      <c r="W1" s="15" t="s">
+      <c r="X1" s="17" t="s">
         <v>453</v>
       </c>
-      <c r="X1" s="17" t="s">
+      <c r="Y1" s="15" t="s">
         <v>454</v>
       </c>
-      <c r="Y1" s="15" t="s">
+      <c r="Z1" s="15" t="s">
         <v>455</v>
       </c>
-      <c r="Z1" s="15" t="s">
+      <c r="AA1" s="17" t="s">
         <v>456</v>
       </c>
-      <c r="AA1" s="17" t="s">
+      <c r="AB1" s="15" t="s">
         <v>457</v>
       </c>
-      <c r="AB1" s="15" t="s">
+      <c r="AC1" s="15" t="s">
         <v>458</v>
       </c>
-      <c r="AC1" s="15" t="s">
+      <c r="AD1" s="15" t="s">
         <v>459</v>
       </c>
-      <c r="AD1" s="15" t="s">
+      <c r="AE1" s="15" t="s">
         <v>460</v>
       </c>
-      <c r="AE1" s="15" t="s">
+      <c r="AF1" s="15" t="s">
         <v>461</v>
       </c>
-      <c r="AF1" s="15" t="s">
+      <c r="AG1" s="15" t="s">
         <v>462</v>
       </c>
-      <c r="AG1" s="15" t="s">
+      <c r="AH1" s="15" t="s">
         <v>463</v>
       </c>
-      <c r="AH1" s="15" t="s">
+      <c r="AI1" s="15" t="s">
         <v>464</v>
       </c>
-      <c r="AI1" s="15" t="s">
+      <c r="AJ1" s="15" t="s">
         <v>465</v>
       </c>
-      <c r="AJ1" s="15" t="s">
+      <c r="AK1" s="15" t="s">
         <v>466</v>
       </c>
-      <c r="AK1" s="15" t="s">
+      <c r="AL1" s="15" t="s">
         <v>467</v>
       </c>
-      <c r="AL1" s="15" t="s">
+      <c r="AM1" s="15" t="s">
         <v>468</v>
       </c>
-      <c r="AM1" s="15" t="s">
+      <c r="AN1" s="15" t="s">
         <v>469</v>
       </c>
-      <c r="AN1" s="15" t="s">
+      <c r="AO1" s="15" t="s">
         <v>470</v>
       </c>
-      <c r="AO1" s="15" t="s">
+      <c r="AP1" s="15" t="s">
         <v>471</v>
       </c>
-      <c r="AP1" s="15" t="s">
+      <c r="AQ1" s="15" t="s">
         <v>472</v>
       </c>
-      <c r="AQ1" s="15" t="s">
+      <c r="AR1" s="15" t="s">
         <v>473</v>
       </c>
-      <c r="AR1" s="15" t="s">
+      <c r="AS1" s="15" t="s">
         <v>474</v>
       </c>
-      <c r="AS1" s="15" t="s">
+      <c r="AT1" s="15" t="s">
         <v>475</v>
       </c>
-      <c r="AT1" s="15" t="s">
+      <c r="AU1" s="15" t="s">
         <v>476</v>
       </c>
-      <c r="AU1" s="15" t="s">
+      <c r="AV1" s="15" t="s">
         <v>477</v>
       </c>
-      <c r="AV1" s="15" t="s">
+      <c r="AW1" s="15" t="s">
         <v>478</v>
       </c>
-      <c r="AW1" s="15" t="s">
+      <c r="AX1" s="18" t="s">
         <v>479</v>
-      </c>
-      <c r="AX1" s="18" t="s">
-        <v>480</v>
       </c>
     </row>
   </sheetData>
